--- a/03_김현우_Ensemble/results/submission.xlsx
+++ b/03_김현우_Ensemble/results/submission.xlsx
@@ -476,22 +476,22 @@
         <v>29400</v>
       </c>
       <c r="D2" t="n">
-        <v>34020.96875</v>
+        <v>35280.93359375</v>
       </c>
       <c r="E2" t="n">
-        <v>9.450269097222222</v>
+        <v>9.800259331597223</v>
       </c>
       <c r="F2" t="n">
-        <v>36215.703125</v>
+        <v>35696.390625</v>
       </c>
       <c r="G2" t="n">
-        <v>32269.82745628351</v>
+        <v>33464.33679466242</v>
       </c>
       <c r="H2" t="n">
         <v>0.221550315618515</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -507,22 +507,22 @@
         <v>29400</v>
       </c>
       <c r="D3" t="n">
-        <v>34572.5234375</v>
+        <v>34980.78125</v>
       </c>
       <c r="E3" t="n">
-        <v>9.603478732638889</v>
+        <v>9.716883680555556</v>
       </c>
       <c r="F3" t="n">
-        <v>37093.46484375</v>
+        <v>36500.671875</v>
       </c>
       <c r="G3" t="n">
-        <v>32810.87744939816</v>
+        <v>33191.41651189816</v>
       </c>
       <c r="H3" t="n">
         <v>0.4320329427719116</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         <v>29400</v>
       </c>
       <c r="D4" t="n">
-        <v>9110.267578125</v>
+        <v>12740.3818359375</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5306298828125</v>
+        <v>3.538994954427083</v>
       </c>
       <c r="F4" t="n">
-        <v>13143.0849609375</v>
+        <v>15928.431640625</v>
       </c>
       <c r="G4" t="n">
-        <v>6828.178778593962</v>
+        <v>10553.56696218771</v>
       </c>
       <c r="H4" t="n">
         <v>0.2467963695526123</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -569,22 +569,22 @@
         <v>29400</v>
       </c>
       <c r="D5" t="n">
-        <v>16471.2109375</v>
+        <v>17900.32421875</v>
       </c>
       <c r="E5" t="n">
-        <v>4.575336371527778</v>
+        <v>4.972312282986111</v>
       </c>
       <c r="F5" t="n">
-        <v>21285.728515625</v>
+        <v>21539.716796875</v>
       </c>
       <c r="G5" t="n">
-        <v>14549.45294180851</v>
+        <v>16053.66265860538</v>
       </c>
       <c r="H5" t="n">
         <v>0.03627244010567665</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -600,22 +600,22 @@
         <v>29400</v>
       </c>
       <c r="D6" t="n">
-        <v>17112.421875</v>
+        <v>18522.986328125</v>
       </c>
       <c r="E6" t="n">
-        <v>4.753450520833334</v>
+        <v>5.145273980034722</v>
       </c>
       <c r="F6" t="n">
-        <v>19516.513671875</v>
+        <v>19912.083984375</v>
       </c>
       <c r="G6" t="n">
-        <v>14872.1531687332</v>
+        <v>16371.52609353789</v>
       </c>
       <c r="H6" t="n">
         <v>0.4668095707893372</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -631,22 +631,22 @@
         <v>29400</v>
       </c>
       <c r="D7" t="n">
-        <v>14864.1953125</v>
+        <v>15717.708984375</v>
       </c>
       <c r="E7" t="n">
-        <v>4.128943142361111</v>
+        <v>4.3660302734375</v>
       </c>
       <c r="F7" t="n">
-        <v>16973.970703125</v>
+        <v>17978.00390625</v>
       </c>
       <c r="G7" t="n">
-        <v>12614.51466020146</v>
+        <v>13553.90211137334</v>
       </c>
       <c r="H7" t="n">
         <v>0.3423601686954498</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/03_김현우_Ensemble/results/submission.xlsx
+++ b/03_김현우_Ensemble/results/submission.xlsx
@@ -476,22 +476,22 @@
         <v>29400</v>
       </c>
       <c r="D2" t="n">
-        <v>35280.93359375</v>
+        <v>33039.4921875</v>
       </c>
       <c r="E2" t="n">
-        <v>9.800259331597223</v>
+        <v>9.17763671875</v>
       </c>
       <c r="F2" t="n">
-        <v>35696.390625</v>
+        <v>34977.85546875</v>
       </c>
       <c r="G2" t="n">
-        <v>33464.33679466242</v>
+        <v>31123.04474143976</v>
       </c>
       <c r="H2" t="n">
         <v>0.221550315618515</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -507,22 +507,22 @@
         <v>29400</v>
       </c>
       <c r="D3" t="n">
-        <v>34980.78125</v>
+        <v>35380.921875</v>
       </c>
       <c r="E3" t="n">
-        <v>9.716883680555556</v>
+        <v>9.828033854166666</v>
       </c>
       <c r="F3" t="n">
-        <v>36500.671875</v>
+        <v>37724.34765625</v>
       </c>
       <c r="G3" t="n">
-        <v>33191.41651189816</v>
+        <v>33413.46869695676</v>
       </c>
       <c r="H3" t="n">
         <v>0.4320329427719116</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         <v>29400</v>
       </c>
       <c r="D4" t="n">
-        <v>12740.3818359375</v>
+        <v>16470.80859375</v>
       </c>
       <c r="E4" t="n">
-        <v>3.538994954427083</v>
+        <v>4.575224609375</v>
       </c>
       <c r="F4" t="n">
-        <v>15928.431640625</v>
+        <v>16526.43359375</v>
       </c>
       <c r="G4" t="n">
-        <v>10553.56696218771</v>
+        <v>14504.58215994162</v>
       </c>
       <c r="H4" t="n">
         <v>0.2467963695526123</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -569,22 +569,22 @@
         <v>29400</v>
       </c>
       <c r="D5" t="n">
-        <v>17900.32421875</v>
+        <v>18457.01171875</v>
       </c>
       <c r="E5" t="n">
-        <v>4.972312282986111</v>
+        <v>5.126947699652778</v>
       </c>
       <c r="F5" t="n">
-        <v>21539.716796875</v>
+        <v>20188.625</v>
       </c>
       <c r="G5" t="n">
-        <v>16053.66265860538</v>
+        <v>16693.7033690546</v>
       </c>
       <c r="H5" t="n">
         <v>0.03627244010567665</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -600,22 +600,22 @@
         <v>29400</v>
       </c>
       <c r="D6" t="n">
-        <v>18522.986328125</v>
+        <v>19227.46875</v>
       </c>
       <c r="E6" t="n">
-        <v>5.145273980034722</v>
+        <v>5.340963541666667</v>
       </c>
       <c r="F6" t="n">
-        <v>19912.083984375</v>
+        <v>19902.109375</v>
       </c>
       <c r="G6" t="n">
-        <v>16371.52609353789</v>
+        <v>17209.25540261992</v>
       </c>
       <c r="H6" t="n">
         <v>0.4668095707893372</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -631,22 +631,22 @@
         <v>29400</v>
       </c>
       <c r="D7" t="n">
-        <v>15717.708984375</v>
+        <v>20017.98828125</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3660302734375</v>
+        <v>5.560552300347222</v>
       </c>
       <c r="F7" t="n">
-        <v>17978.00390625</v>
+        <v>20311.01171875</v>
       </c>
       <c r="G7" t="n">
-        <v>13553.90211137334</v>
+        <v>17836.46986039677</v>
       </c>
       <c r="H7" t="n">
         <v>0.3423601686954498</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/03_김현우_Ensemble/results/submission.xlsx
+++ b/03_김현우_Ensemble/results/submission.xlsx
@@ -476,22 +476,22 @@
         <v>29400</v>
       </c>
       <c r="D2" t="n">
-        <v>33039.4921875</v>
+        <v>32081.17578125</v>
       </c>
       <c r="E2" t="n">
-        <v>9.17763671875</v>
+        <v>8.911437717013889</v>
       </c>
       <c r="F2" t="n">
-        <v>34977.85546875</v>
+        <v>34867.28125</v>
       </c>
       <c r="G2" t="n">
-        <v>31123.04474143976</v>
+        <v>30276.91260032648</v>
       </c>
       <c r="H2" t="n">
         <v>0.221550315618515</v>
       </c>
       <c r="I2" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -507,22 +507,22 @@
         <v>29400</v>
       </c>
       <c r="D3" t="n">
-        <v>35380.921875</v>
+        <v>33519.3515625</v>
       </c>
       <c r="E3" t="n">
-        <v>9.828033854166666</v>
+        <v>9.310930989583333</v>
       </c>
       <c r="F3" t="n">
-        <v>37724.34765625</v>
+        <v>35668.32421875</v>
       </c>
       <c r="G3" t="n">
-        <v>33413.46869695676</v>
+        <v>31644.05439031613</v>
       </c>
       <c r="H3" t="n">
         <v>0.4320329427719116</v>
       </c>
       <c r="I3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -538,22 +538,22 @@
         <v>29400</v>
       </c>
       <c r="D4" t="n">
-        <v>16470.80859375</v>
+        <v>7778.1416015625</v>
       </c>
       <c r="E4" t="n">
-        <v>4.575224609375</v>
+        <v>2.160594889322917</v>
       </c>
       <c r="F4" t="n">
-        <v>16526.43359375</v>
+        <v>10197.79296875</v>
       </c>
       <c r="G4" t="n">
-        <v>14504.58215994162</v>
+        <v>5724.486884062712</v>
       </c>
       <c r="H4" t="n">
         <v>0.2467963695526123</v>
       </c>
       <c r="I4" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -569,22 +569,22 @@
         <v>29400</v>
       </c>
       <c r="D5" t="n">
-        <v>18457.01171875</v>
+        <v>14910.0341796875</v>
       </c>
       <c r="E5" t="n">
-        <v>5.126947699652778</v>
+        <v>4.141676161024305</v>
       </c>
       <c r="F5" t="n">
-        <v>20188.625</v>
+        <v>18841.48828125</v>
       </c>
       <c r="G5" t="n">
-        <v>16693.7033690546</v>
+        <v>13105.61029044132</v>
       </c>
       <c r="H5" t="n">
         <v>0.03627244010567665</v>
       </c>
       <c r="I5" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -600,22 +600,22 @@
         <v>29400</v>
       </c>
       <c r="D6" t="n">
-        <v>19227.46875</v>
+        <v>15525.8984375</v>
       </c>
       <c r="E6" t="n">
-        <v>5.340963541666667</v>
+        <v>4.312749565972222</v>
       </c>
       <c r="F6" t="n">
-        <v>19902.109375</v>
+        <v>17378.8828125</v>
       </c>
       <c r="G6" t="n">
-        <v>17209.25540261992</v>
+        <v>13562.34451394805</v>
       </c>
       <c r="H6" t="n">
         <v>0.4668095707893372</v>
       </c>
       <c r="I6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -631,22 +631,22 @@
         <v>29400</v>
       </c>
       <c r="D7" t="n">
-        <v>20017.98828125</v>
+        <v>12122.189453125</v>
       </c>
       <c r="E7" t="n">
-        <v>5.560552300347222</v>
+        <v>3.367274848090278</v>
       </c>
       <c r="F7" t="n">
-        <v>20311.01171875</v>
+        <v>14776.966796875</v>
       </c>
       <c r="G7" t="n">
-        <v>17836.46986039677</v>
+        <v>9509.956615767867</v>
       </c>
       <c r="H7" t="n">
         <v>0.3423601686954498</v>
       </c>
       <c r="I7" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/03_김현우_Ensemble/results/submission.xlsx
+++ b/03_김현우_Ensemble/results/submission.xlsx
@@ -476,16 +476,16 @@
         <v>29400</v>
       </c>
       <c r="D2" t="n">
-        <v>32081.17578125</v>
+        <v>31309.81640625</v>
       </c>
       <c r="E2" t="n">
-        <v>8.911437717013889</v>
+        <v>8.697171223958334</v>
       </c>
       <c r="F2" t="n">
-        <v>34867.28125</v>
+        <v>34031.97265625</v>
       </c>
       <c r="G2" t="n">
-        <v>30276.91260032648</v>
+        <v>29525.92804222101</v>
       </c>
       <c r="H2" t="n">
         <v>0.221550315618515</v>
@@ -507,16 +507,16 @@
         <v>29400</v>
       </c>
       <c r="D3" t="n">
-        <v>33519.3515625</v>
+        <v>32040.50390625</v>
       </c>
       <c r="E3" t="n">
-        <v>9.310930989583333</v>
+        <v>8.900139973958334</v>
       </c>
       <c r="F3" t="n">
-        <v>35668.32421875</v>
+        <v>34442.2578125</v>
       </c>
       <c r="G3" t="n">
-        <v>31644.05439031613</v>
+        <v>30134.53174627316</v>
       </c>
       <c r="H3" t="n">
         <v>0.4320329427719116</v>
@@ -538,16 +538,16 @@
         <v>29400</v>
       </c>
       <c r="D4" t="n">
-        <v>7778.1416015625</v>
+        <v>6528.830078125</v>
       </c>
       <c r="E4" t="n">
-        <v>2.160594889322917</v>
+        <v>1.813563910590278</v>
       </c>
       <c r="F4" t="n">
-        <v>10197.79296875</v>
+        <v>9391.94140625</v>
       </c>
       <c r="G4" t="n">
-        <v>5724.486884062712</v>
+        <v>4536.519354765837</v>
       </c>
       <c r="H4" t="n">
         <v>0.2467963695526123</v>
@@ -569,16 +569,16 @@
         <v>29400</v>
       </c>
       <c r="D5" t="n">
-        <v>14910.0341796875</v>
+        <v>16029.5205078125</v>
       </c>
       <c r="E5" t="n">
-        <v>4.141676161024305</v>
+        <v>4.452644585503473</v>
       </c>
       <c r="F5" t="n">
-        <v>18841.48828125</v>
+        <v>18945.71484375</v>
       </c>
       <c r="G5" t="n">
-        <v>13105.61029044132</v>
+        <v>14259.53015128116</v>
       </c>
       <c r="H5" t="n">
         <v>0.03627244010567665</v>
@@ -600,16 +600,16 @@
         <v>29400</v>
       </c>
       <c r="D6" t="n">
-        <v>15525.8984375</v>
+        <v>15958.5546875</v>
       </c>
       <c r="E6" t="n">
-        <v>4.312749565972222</v>
+        <v>4.432931857638889</v>
       </c>
       <c r="F6" t="n">
-        <v>17378.8828125</v>
+        <v>17511.533203125</v>
       </c>
       <c r="G6" t="n">
-        <v>13562.34451394805</v>
+        <v>14153.42923074492</v>
       </c>
       <c r="H6" t="n">
         <v>0.4668095707893372</v>
@@ -631,16 +631,16 @@
         <v>29400</v>
       </c>
       <c r="D7" t="n">
-        <v>12122.189453125</v>
+        <v>11988.783203125</v>
       </c>
       <c r="E7" t="n">
-        <v>3.367274848090278</v>
+        <v>3.330217556423611</v>
       </c>
       <c r="F7" t="n">
-        <v>14776.966796875</v>
+        <v>17769.248046875</v>
       </c>
       <c r="G7" t="n">
-        <v>9509.956615767867</v>
+        <v>9109.094555220992</v>
       </c>
       <c r="H7" t="n">
         <v>0.3423601686954498</v>

--- a/03_김현우_Ensemble/results/submission.xlsx
+++ b/03_김현우_Ensemble/results/submission.xlsx
@@ -476,16 +476,16 @@
         <v>29400</v>
       </c>
       <c r="D2" t="n">
-        <v>31309.81640625</v>
+        <v>32171.724609375</v>
       </c>
       <c r="E2" t="n">
-        <v>8.697171223958334</v>
+        <v>8.936590169270833</v>
       </c>
       <c r="F2" t="n">
-        <v>34031.97265625</v>
+        <v>34036.46484375</v>
       </c>
       <c r="G2" t="n">
-        <v>29525.92804222101</v>
+        <v>30295.80761985773</v>
       </c>
       <c r="H2" t="n">
         <v>0.221550315618515</v>
@@ -507,16 +507,16 @@
         <v>29400</v>
       </c>
       <c r="D3" t="n">
-        <v>32040.50390625</v>
+        <v>33102.015625</v>
       </c>
       <c r="E3" t="n">
-        <v>8.900139973958334</v>
+        <v>9.195004340277778</v>
       </c>
       <c r="F3" t="n">
-        <v>34442.2578125</v>
+        <v>34696.6171875</v>
       </c>
       <c r="G3" t="n">
-        <v>30134.53174627316</v>
+        <v>31155.85688055051</v>
       </c>
       <c r="H3" t="n">
         <v>0.4320329427719116</v>
@@ -538,16 +538,16 @@
         <v>29400</v>
       </c>
       <c r="D4" t="n">
-        <v>6528.830078125</v>
+        <v>7008.36669921875</v>
       </c>
       <c r="E4" t="n">
-        <v>1.813563910590278</v>
+        <v>1.946768527560764</v>
       </c>
       <c r="F4" t="n">
-        <v>9391.94140625</v>
+        <v>8994.220703125</v>
       </c>
       <c r="G4" t="n">
-        <v>4536.519354765837</v>
+        <v>5128.783026640837</v>
       </c>
       <c r="H4" t="n">
         <v>0.2467963695526123</v>
@@ -569,16 +569,16 @@
         <v>29400</v>
       </c>
       <c r="D5" t="n">
-        <v>16029.5205078125</v>
+        <v>15206.080078125</v>
       </c>
       <c r="E5" t="n">
-        <v>4.452644585503473</v>
+        <v>4.2239111328125</v>
       </c>
       <c r="F5" t="n">
-        <v>18945.71484375</v>
+        <v>17584.29296875</v>
       </c>
       <c r="G5" t="n">
-        <v>14259.53015128116</v>
+        <v>13426.87927237491</v>
       </c>
       <c r="H5" t="n">
         <v>0.03627244010567665</v>
@@ -600,16 +600,16 @@
         <v>29400</v>
       </c>
       <c r="D6" t="n">
-        <v>15958.5546875</v>
+        <v>14928.185546875</v>
       </c>
       <c r="E6" t="n">
-        <v>4.432931857638889</v>
+        <v>4.146718207465278</v>
       </c>
       <c r="F6" t="n">
-        <v>17511.533203125</v>
+        <v>15904.287109375</v>
       </c>
       <c r="G6" t="n">
-        <v>14153.42923074492</v>
+        <v>13068.38809304961</v>
       </c>
       <c r="H6" t="n">
         <v>0.4668095707893372</v>
@@ -631,16 +631,16 @@
         <v>29400</v>
       </c>
       <c r="D7" t="n">
-        <v>11988.783203125</v>
+        <v>11515.767578125</v>
       </c>
       <c r="E7" t="n">
-        <v>3.330217556423611</v>
+        <v>3.198824327256944</v>
       </c>
       <c r="F7" t="n">
-        <v>17769.248046875</v>
+        <v>16398.78515625</v>
       </c>
       <c r="G7" t="n">
-        <v>9109.094555220992</v>
+        <v>8683.539135299117</v>
       </c>
       <c r="H7" t="n">
         <v>0.3423601686954498</v>
